--- a/test_codes/百度表格-修复版.xlsx
+++ b/test_codes/百度表格-修复版.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,8 +47,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -416,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -427,290 +431,722 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2023年12月31日</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>产品发行募集</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>产品到期兑付</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>(人民币百万元，期数除外)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>期数
+金额</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>期数
+金额</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>期数
+金额</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>期数
+金额</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>建信理财</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1,100</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1,499,121</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,315,531</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,215,927</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,598,725</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>本行</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>79,443</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>101,819</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>138,974</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,288</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>总额</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1,102</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1,578,564</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,417,350</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,354,901</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,641,013</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>建信理财</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024年12月31日
+本行</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>建信理财</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>2023年12月31日
+本行</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>(人民币百万元，百分比除外)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>金额
+占比(%)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>占比(%)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>金额
+占比(%)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>金额
+占比(%)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>金额
+占比(%)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>金额
+占比(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>现金、存款及同业存单</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1,008,220</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>60.80</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>20,512</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>34.60</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1,028,732</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>59.90</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>907,809</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>58.73</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>31,462</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>32.01</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>939,271</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>57.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>债券</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>440,983</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,052</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8.52</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>446,035</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25.97</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>478,169</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30.94</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7,942</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8.08</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>486,111</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>权益类资产</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1,793</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25,679</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43.31</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27,472</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,643</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>11,799</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12.01</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>35,442</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>非标准化债权类资产</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5,171</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,042</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13.57</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13,213</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,714</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>43,586</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>44.35</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>55,300</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="1" t="n"/>
-      <c r="C7" s="1" t="n"/>
-      <c r="D7" s="1" t="n"/>
-      <c r="E7" s="1" t="n"/>
-      <c r="F7" s="1" t="n"/>
-      <c r="G7" s="1" t="n"/>
-      <c r="H7" s="1" t="n"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>其他类资产！</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>201,987</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12.18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>201,987</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11.76</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>124,247</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8.04</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3,492</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>127,739</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7.77</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1" t="n"/>
-      <c r="G8" s="1" t="n"/>
-      <c r="H8" s="1" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="n"/>
-      <c r="C9" s="1" t="n"/>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="1" t="n"/>
-      <c r="E10" s="1" t="n"/>
-      <c r="F10" s="1" t="n"/>
-      <c r="G10" s="1" t="n"/>
-      <c r="H10" s="1" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="1" t="n"/>
-      <c r="E11" s="1" t="n"/>
-      <c r="F11" s="1" t="n"/>
-      <c r="G11" s="1" t="n"/>
-      <c r="H11" s="1" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="1" t="n"/>
-      <c r="C12" s="1" t="n"/>
-      <c r="D12" s="1" t="n"/>
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
-      <c r="E13" s="1" t="n"/>
-      <c r="F13" s="1" t="n"/>
-      <c r="G13" s="1" t="n"/>
-      <c r="H13" s="1" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="1" t="n"/>
-      <c r="E14" s="1" t="n"/>
-      <c r="F14" s="1" t="n"/>
-      <c r="G14" s="1" t="n"/>
-      <c r="H14" s="1" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="1" t="n"/>
-      <c r="E15" s="1" t="n"/>
-      <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
-      <c r="G16" s="1" t="n"/>
-      <c r="H16" s="1" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
-      <c r="E17" s="1" t="n"/>
-      <c r="F17" s="1" t="n"/>
-      <c r="G17" s="1" t="n"/>
-      <c r="H17" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>总额</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1,658,154</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59,285</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,717,439</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,545,582</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>98,281</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1,643,863</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="109">
-    <mergeCell ref="D3:E4"/>
-    <mergeCell ref="D12:E13"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="A10:B11"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="F4:G5"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="G2:H3"/>
-    <mergeCell ref="G11:H12"/>
-    <mergeCell ref="F15:G16"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E6:F7"/>
-    <mergeCell ref="G6:H7"/>
-    <mergeCell ref="E15:F16"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="B9:C10"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="D14:E15"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="D6:E7"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E10:F11"/>
-    <mergeCell ref="G10:H11"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G3:H4"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="D4:E5"/>
-    <mergeCell ref="D16:E17"/>
-    <mergeCell ref="A2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:F3"/>
-    <mergeCell ref="C11:D12"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="G5:H6"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="D1:F2"/>
-    <mergeCell ref="F1:H2"/>
-    <mergeCell ref="D8:E9"/>
-    <mergeCell ref="G4:H5"/>
-    <mergeCell ref="D10:E11"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="F16:G17"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H14"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="F2:G3"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="B13:C14"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="F10:G11"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="A11:B12"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E5:F6"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="B8:C9"/>
-    <mergeCell ref="E4:F5"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:E3"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F5:G6"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>